--- a/artfynd/A 16904-2025 artfynd.xlsx
+++ b/artfynd/A 16904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128648744</v>
       </c>
       <c r="B2" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128648831</v>
       </c>
       <c r="B3" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128648787</v>
       </c>
       <c r="B4" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128630503</v>
+        <v>128648818</v>
       </c>
       <c r="B5" t="n">
-        <v>56566</v>
+        <v>57686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1031,25 +1031,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Drängsbo-Lilla Gullringsvatten , Ög</t>
+          <t>Drängsbo-Lilla Gullringsvattnet, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567314</v>
+        <v>567313</v>
       </c>
       <c r="R5" t="n">
-        <v>6456972</v>
+        <v>6456888</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,17 +1083,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Den har nog sin hemvist dvs. övernattningsplatsen i kontinuitetsskogen</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,53 +1115,58 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128648922</v>
+        <v>128630503</v>
       </c>
       <c r="B6" t="n">
-        <v>98572</v>
+        <v>56570</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Drängsbo-Lilla Gullringsvattnet, Ög</t>
+          <t>Drängsbo-Lilla Gullringsvatten , Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567215</v>
+        <v>567314</v>
       </c>
       <c r="R6" t="n">
-        <v>6456852</v>
+        <v>6456972</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,17 +1193,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Mycket små plantor och lite svår att upptäcka.</t>
+          <t>Den har nog sin hemvist dvs. övernattningsplatsen i kontinuitetsskogen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1212,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1224,54 +1230,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128648818</v>
+        <v>128648922</v>
       </c>
       <c r="B7" t="n">
-        <v>57682</v>
+        <v>98579</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1279,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567313</v>
+        <v>567215</v>
       </c>
       <c r="R7" t="n">
-        <v>6456888</v>
+        <v>6456852</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1317,12 +1311,18 @@
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mycket små plantor och lite svår att upptäcka.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1341,42 +1341,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128648939</v>
+        <v>128648941</v>
       </c>
       <c r="B8" t="n">
-        <v>98572</v>
+        <v>91478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1447,41 +1446,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128648941</v>
+        <v>128648939</v>
       </c>
       <c r="B9" t="n">
-        <v>91473</v>
+        <v>98579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128648853</v>
       </c>
       <c r="B10" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128648835</v>
       </c>
       <c r="B11" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128649132</v>
+        <v>128648847</v>
       </c>
       <c r="B12" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567329</v>
+        <v>567262</v>
       </c>
       <c r="R12" t="n">
-        <v>6456822</v>
+        <v>6456876</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128648847</v>
+        <v>128649132</v>
       </c>
       <c r="B13" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567262</v>
+        <v>567329</v>
       </c>
       <c r="R13" t="n">
-        <v>6456876</v>
+        <v>6456822</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1978,7 +1978,7 @@
         <v>128648990</v>
       </c>
       <c r="B14" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128648966</v>
       </c>
       <c r="B15" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128648931</v>
       </c>
       <c r="B16" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,10 +2309,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128648974</v>
+        <v>128648804</v>
       </c>
       <c r="B17" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567268</v>
+        <v>567313</v>
       </c>
       <c r="R17" t="n">
-        <v>6456816</v>
+        <v>6456888</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128648804</v>
+        <v>128648974</v>
       </c>
       <c r="B18" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567313</v>
+        <v>567268</v>
       </c>
       <c r="R18" t="n">
-        <v>6456888</v>
+        <v>6456816</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2524,7 +2524,7 @@
         <v>128648979</v>
       </c>
       <c r="B19" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>128648897</v>
       </c>
       <c r="B20" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128630164</v>
       </c>
       <c r="B21" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 16904-2025 artfynd.xlsx
+++ b/artfynd/A 16904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128648744</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128648831</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128648787</v>
       </c>
       <c r="B4" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128648922</v>
       </c>
       <c r="B7" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>128648941</v>
       </c>
       <c r="B8" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128648939</v>
       </c>
       <c r="B9" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128648853</v>
       </c>
       <c r="B10" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128648835</v>
       </c>
       <c r="B11" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128648847</v>
       </c>
       <c r="B12" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128649132</v>
       </c>
       <c r="B13" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128648990</v>
       </c>
       <c r="B14" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128648931</v>
       </c>
       <c r="B16" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>128648804</v>
       </c>
       <c r="B17" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>128648974</v>
       </c>
       <c r="B18" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>128648979</v>
       </c>
       <c r="B19" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 16904-2025 artfynd.xlsx
+++ b/artfynd/A 16904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128648744</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128648831</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128648787</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128648922</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>128648941</v>
       </c>
       <c r="B8" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128648939</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128648853</v>
       </c>
       <c r="B10" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128648835</v>
       </c>
       <c r="B11" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128648847</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128649132</v>
       </c>
       <c r="B13" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128648990</v>
       </c>
       <c r="B14" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128648931</v>
       </c>
       <c r="B16" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>128648804</v>
       </c>
       <c r="B17" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>128648974</v>
       </c>
       <c r="B18" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>128648979</v>
       </c>
       <c r="B19" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 16904-2025 artfynd.xlsx
+++ b/artfynd/A 16904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128648744</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128648831</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128648787</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128648922</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128648939</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128648853</v>
       </c>
       <c r="B10" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128648847</v>
       </c>
       <c r="B12" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128649132</v>
       </c>
       <c r="B13" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128648990</v>
       </c>
       <c r="B14" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128648931</v>
       </c>
       <c r="B16" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>128648804</v>
       </c>
       <c r="B17" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>128648974</v>
       </c>
       <c r="B18" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 16904-2025 artfynd.xlsx
+++ b/artfynd/A 16904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128648744</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128648831</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128648787</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128648922</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>128648941</v>
       </c>
       <c r="B8" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128648939</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128648853</v>
       </c>
       <c r="B10" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128648835</v>
       </c>
       <c r="B11" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128648847</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128649132</v>
       </c>
       <c r="B13" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128648990</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128648931</v>
       </c>
       <c r="B16" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>128648804</v>
       </c>
       <c r="B17" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>128648974</v>
       </c>
       <c r="B18" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>128648979</v>
       </c>
       <c r="B19" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 16904-2025 artfynd.xlsx
+++ b/artfynd/A 16904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128648744</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128648831</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128648787</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128648818</v>
       </c>
       <c r="B5" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128630503</v>
       </c>
       <c r="B6" t="n">
-        <v>56570</v>
+        <v>56597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128648922</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>128648941</v>
       </c>
       <c r="B8" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128648939</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128648853</v>
       </c>
       <c r="B10" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128648835</v>
       </c>
       <c r="B11" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128648847</v>
       </c>
       <c r="B12" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128649132</v>
       </c>
       <c r="B13" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128648990</v>
       </c>
       <c r="B14" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128648966</v>
       </c>
       <c r="B15" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128648931</v>
       </c>
       <c r="B16" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>128648804</v>
       </c>
       <c r="B17" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>128648974</v>
       </c>
       <c r="B18" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>128648979</v>
       </c>
       <c r="B19" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>128648897</v>
       </c>
       <c r="B20" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128630164</v>
       </c>
       <c r="B21" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 16904-2025 artfynd.xlsx
+++ b/artfynd/A 16904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128648744</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128648831</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128648787</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128648922</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>128648941</v>
       </c>
       <c r="B8" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128648939</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128648853</v>
       </c>
       <c r="B10" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128648835</v>
       </c>
       <c r="B11" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128648847</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128649132</v>
       </c>
       <c r="B13" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128648990</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128648931</v>
       </c>
       <c r="B16" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>128648804</v>
       </c>
       <c r="B17" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>128648974</v>
       </c>
       <c r="B18" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>128648979</v>
       </c>
       <c r="B19" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 16904-2025 artfynd.xlsx
+++ b/artfynd/A 16904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128648744</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128648831</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128648787</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128648922</v>
       </c>
       <c r="B7" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>128648941</v>
       </c>
       <c r="B8" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128648939</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128648853</v>
       </c>
       <c r="B10" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128648835</v>
       </c>
       <c r="B11" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128648847</v>
       </c>
       <c r="B12" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128649132</v>
       </c>
       <c r="B13" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128648990</v>
       </c>
       <c r="B14" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128648931</v>
       </c>
       <c r="B16" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>128648804</v>
       </c>
       <c r="B17" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>128648974</v>
       </c>
       <c r="B18" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>128648979</v>
       </c>
       <c r="B19" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 16904-2025 artfynd.xlsx
+++ b/artfynd/A 16904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128648744</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128648831</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128648787</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128648818</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128630503</v>
       </c>
       <c r="B6" t="n">
-        <v>56597</v>
+        <v>56600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128648922</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>128648941</v>
       </c>
       <c r="B8" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128648939</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128648853</v>
       </c>
       <c r="B10" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128648835</v>
       </c>
       <c r="B11" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128648847</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128649132</v>
       </c>
       <c r="B13" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128648990</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128648966</v>
       </c>
       <c r="B15" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128648931</v>
       </c>
       <c r="B16" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>128648804</v>
       </c>
       <c r="B17" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>128648974</v>
       </c>
       <c r="B18" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>128648979</v>
       </c>
       <c r="B19" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>128648897</v>
       </c>
       <c r="B20" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128630164</v>
       </c>
       <c r="B21" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 16904-2025 artfynd.xlsx
+++ b/artfynd/A 16904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128648744</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128648831</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128648787</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128648818</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128630503</v>
       </c>
       <c r="B6" t="n">
-        <v>56600</v>
+        <v>56603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128648922</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>128648941</v>
       </c>
       <c r="B8" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128648939</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128648853</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128648835</v>
       </c>
       <c r="B11" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128648847</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128649132</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128648990</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128648966</v>
       </c>
       <c r="B15" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128648931</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>128648804</v>
       </c>
       <c r="B17" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>128648974</v>
       </c>
       <c r="B18" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>128648979</v>
       </c>
       <c r="B19" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>128648897</v>
       </c>
       <c r="B20" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>128630164</v>
       </c>
       <c r="B21" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
